--- a/backend/src/test/resources/golden/radar_pre_t281.xlsx
+++ b/backend/src/test/resources/golden/radar_pre_t281.xlsx
@@ -9,12 +9,13 @@
     <sheet name="快照索引" r:id="rId3" sheetId="1"/>
     <sheet name="大盤總覽" r:id="rId4" sheetId="2"/>
     <sheet name="個股決策" r:id="rId5" sheetId="3"/>
+    <sheet name="台美公開資訊" r:id="rId6" sheetId="4"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="134">
   <si>
     <t>查得 1 筆／索引預期 2 筆／缺漏 1 筆（已逾期或被 LRU 逐出）</t>
   </si>
@@ -40,7 +41,7 @@
     <t>個股檔數</t>
   </si>
   <si>
-    <t>略過非台股檔數</t>
+    <t>略過非台股非美股檔數</t>
   </si>
   <si>
     <t>2026-07-31T13:30:00</t>
@@ -88,6 +89,12 @@
     <t>漲跌%</t>
   </si>
   <si>
+    <t>行情狀態</t>
+  </si>
+  <si>
+    <t>週線MA5</t>
+  </si>
+  <si>
     <t>MA20</t>
   </si>
   <si>
@@ -109,6 +116,72 @@
     <t>D</t>
   </si>
   <si>
+    <t>J9</t>
+  </si>
+  <si>
+    <t>K3D2</t>
+  </si>
+  <si>
+    <t>RSV</t>
+  </si>
+  <si>
+    <t>EMA12</t>
+  </si>
+  <si>
+    <t>EMA26</t>
+  </si>
+  <si>
+    <t>DIF</t>
+  </si>
+  <si>
+    <t>MACD</t>
+  </si>
+  <si>
+    <t>OSC</t>
+  </si>
+  <si>
+    <t>RSI5</t>
+  </si>
+  <si>
+    <t>RSI10</t>
+  </si>
+  <si>
+    <t>BIAS10</t>
+  </si>
+  <si>
+    <t>BIAS20</t>
+  </si>
+  <si>
+    <t>BIAS10-BIAS20</t>
+  </si>
+  <si>
+    <t>W%R9</t>
+  </si>
+  <si>
+    <t>大盤量比</t>
+  </si>
+  <si>
+    <t>大盤成交金額比</t>
+  </si>
+  <si>
+    <t>量能完成日</t>
+  </si>
+  <si>
+    <t>NASDAQ漲跌%</t>
+  </si>
+  <si>
+    <t>SOX漲跌%</t>
+  </si>
+  <si>
+    <t>美股科技綜合%</t>
+  </si>
+  <si>
+    <t>美股科技完成日</t>
+  </si>
+  <si>
+    <t>美股科技可用</t>
+  </si>
+  <si>
     <t>支持訊號</t>
   </si>
   <si>
@@ -124,6 +197,9 @@
     <t>2026-07-30</t>
   </si>
   <si>
+    <t>VERIFIED_CLOSE</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
@@ -145,10 +221,28 @@
     <t>還原權息</t>
   </si>
   <si>
-    <t>動作</t>
-  </si>
-  <si>
-    <t>動作中文</t>
+    <t>短期動作</t>
+  </si>
+  <si>
+    <t>短期動作中文</t>
+  </si>
+  <si>
+    <t>短期分數</t>
+  </si>
+  <si>
+    <t>中期動作</t>
+  </si>
+  <si>
+    <t>中期動作中文</t>
+  </si>
+  <si>
+    <t>中期分數</t>
+  </si>
+  <si>
+    <t>短中期分歧</t>
+  </si>
+  <si>
+    <t>獲利了結確認</t>
   </si>
   <si>
     <t>逆勢狀態</t>
@@ -166,9 +260,15 @@
     <t>月線確認</t>
   </si>
   <si>
+    <t>個股量比</t>
+  </si>
+  <si>
     <t>匯率分位</t>
   </si>
   <si>
+    <t>匯率完成日</t>
+  </si>
+  <si>
     <t>底層幣別</t>
   </si>
   <si>
@@ -184,6 +284,102 @@
     <t>折溢價%</t>
   </si>
   <si>
+    <t>基本面適用</t>
+  </si>
+  <si>
+    <t>基本面覆蓋(0-4)</t>
+  </si>
+  <si>
+    <t>EPS TTM年增%</t>
+  </si>
+  <si>
+    <t>EPS來源</t>
+  </si>
+  <si>
+    <t>EPS來源網址</t>
+  </si>
+  <si>
+    <t>EPS資料時點</t>
+  </si>
+  <si>
+    <t>近似ROE%</t>
+  </si>
+  <si>
+    <t>ROE來源</t>
+  </si>
+  <si>
+    <t>ROE來源網址</t>
+  </si>
+  <si>
+    <t>ROE資料時點</t>
+  </si>
+  <si>
+    <t>近3月營收年增%</t>
+  </si>
+  <si>
+    <t>營收來源</t>
+  </si>
+  <si>
+    <t>營收來源網址</t>
+  </si>
+  <si>
+    <t>營收資料時點</t>
+  </si>
+  <si>
+    <t>PE自身分位</t>
+  </si>
+  <si>
+    <t>PE可信虧損</t>
+  </si>
+  <si>
+    <t>估值來源</t>
+  </si>
+  <si>
+    <t>估值來源網址</t>
+  </si>
+  <si>
+    <t>估值資料時點</t>
+  </si>
+  <si>
+    <t>產業</t>
+  </si>
+  <si>
+    <t>產業營收年增%</t>
+  </si>
+  <si>
+    <t>產業公司數</t>
+  </si>
+  <si>
+    <t>產業資料年月</t>
+  </si>
+  <si>
+    <t>產業來源</t>
+  </si>
+  <si>
+    <t>產業來源網址</t>
+  </si>
+  <si>
+    <t>產業資料時點</t>
+  </si>
+  <si>
+    <t>public_info_*個股證據</t>
+  </si>
+  <si>
+    <t>public_info_*產業證據</t>
+  </si>
+  <si>
+    <t>短期支持訊號</t>
+  </si>
+  <si>
+    <t>短期風險提醒</t>
+  </si>
+  <si>
+    <t>中期支持訊號</t>
+  </si>
+  <si>
+    <t>中期風險提醒</t>
+  </si>
+  <si>
     <t>逆勢條件</t>
   </si>
   <si>
@@ -203,14 +399,35 @@
   </si>
   <si>
     <t>回檔買點</t>
+  </si>
+  <si>
+    <t>地區</t>
+  </si>
+  <si>
+    <t>發布時間</t>
+  </si>
+  <si>
+    <t>來源</t>
+  </si>
+  <si>
+    <t>標題</t>
+  </si>
+  <si>
+    <t>摘要</t>
+  </si>
+  <si>
+    <t>網址</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="4">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
+  </numFmts>
+  <fonts count="5">
     <font>
       <sz val="11.0"/>
       <color indexed="8"/>
@@ -221,6 +438,11 @@
     <font>
       <name val="Calibri"/>
       <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="13.0"/>
       <b val="true"/>
     </font>
     <font>
@@ -255,14 +477,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="true"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
   </cellXfs>
 </styleSheet>
 </file>
@@ -279,11 +506,11 @@
     <col min="5" max="5" width="7.2890625" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="8.5546875" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="7.2890625" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="12.03515625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="16.77734375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="s" s="3">
+      <c r="A1" t="s" s="4">
         <v>0</v>
       </c>
     </row>
@@ -326,7 +553,7 @@
       <c r="D3" t="s" s="0">
         <v>12</v>
       </c>
-      <c r="E3" t="n" s="4">
+      <c r="E3" t="n" s="7">
         <v>72.5</v>
       </c>
       <c r="F3" t="s" s="0">
@@ -346,7 +573,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:T2"/>
+  <dimension ref="A1:AR2"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="18.73046875" customWidth="true" bestFit="true"/>
@@ -360,15 +587,39 @@
     <col min="9" max="9" width="10.73046875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="7.2890625" customWidth="true" bestFit="true"/>
     <col min="11" max="11" width="5.3671875" customWidth="true" bestFit="true"/>
-    <col min="12" max="12" width="5.65234375" customWidth="true" bestFit="true"/>
-    <col min="13" max="13" width="5.65234375" customWidth="true" bestFit="true"/>
-    <col min="14" max="14" width="6.6953125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="7.2890625" customWidth="true" bestFit="true"/>
-    <col min="16" max="16" width="7.2890625" customWidth="true" bestFit="true"/>
-    <col min="17" max="17" width="2.0859375" customWidth="true" bestFit="true"/>
-    <col min="18" max="18" width="2.21875" customWidth="true" bestFit="true"/>
-    <col min="19" max="19" width="7.2890625" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="7.2890625" customWidth="true" bestFit="true"/>
+    <col min="12" max="12" width="13.2578125" customWidth="true" bestFit="true"/>
+    <col min="13" max="13" width="8.90234375" customWidth="true" bestFit="true"/>
+    <col min="14" max="14" width="5.65234375" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="5.65234375" customWidth="true" bestFit="true"/>
+    <col min="16" max="16" width="6.6953125" customWidth="true" bestFit="true"/>
+    <col min="17" max="17" width="7.2890625" customWidth="true" bestFit="true"/>
+    <col min="18" max="18" width="7.2890625" customWidth="true" bestFit="true"/>
+    <col min="19" max="19" width="2.0859375" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="2.21875" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="6.40234375" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="6.40234375" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="6.40234375" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="6.6015625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="6.6015625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="6.40234375" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="6.40234375" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="6.40234375" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="6.40234375" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="6.40234375" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="6.640625" customWidth="true" bestFit="true"/>
+    <col min="32" max="32" width="6.640625" customWidth="true" bestFit="true"/>
+    <col min="33" max="33" width="13.32421875" customWidth="true" bestFit="true"/>
+    <col min="34" max="34" width="6.40234375" customWidth="true" bestFit="true"/>
+    <col min="35" max="35" width="7.2890625" customWidth="true" bestFit="true"/>
+    <col min="36" max="36" width="12.03515625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="8.87109375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="12.37109375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="8.625" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="11.69140625" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="12.03515625" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="10.453125" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="7.2890625" customWidth="true" bestFit="true"/>
+    <col min="44" max="44" width="7.2890625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -432,6 +683,78 @@
       <c r="T1" t="s" s="1">
         <v>32</v>
       </c>
+      <c r="U1" t="s" s="1">
+        <v>33</v>
+      </c>
+      <c r="V1" t="s" s="1">
+        <v>34</v>
+      </c>
+      <c r="W1" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="X1" t="s" s="1">
+        <v>36</v>
+      </c>
+      <c r="Y1" t="s" s="1">
+        <v>37</v>
+      </c>
+      <c r="Z1" t="s" s="1">
+        <v>38</v>
+      </c>
+      <c r="AA1" t="s" s="1">
+        <v>39</v>
+      </c>
+      <c r="AB1" t="s" s="1">
+        <v>40</v>
+      </c>
+      <c r="AC1" t="s" s="1">
+        <v>41</v>
+      </c>
+      <c r="AD1" t="s" s="1">
+        <v>42</v>
+      </c>
+      <c r="AE1" t="s" s="1">
+        <v>43</v>
+      </c>
+      <c r="AF1" t="s" s="1">
+        <v>44</v>
+      </c>
+      <c r="AG1" t="s" s="1">
+        <v>45</v>
+      </c>
+      <c r="AH1" t="s" s="1">
+        <v>46</v>
+      </c>
+      <c r="AI1" t="s" s="1">
+        <v>47</v>
+      </c>
+      <c r="AJ1" t="s" s="1">
+        <v>48</v>
+      </c>
+      <c r="AK1" t="s" s="1">
+        <v>49</v>
+      </c>
+      <c r="AL1" t="s" s="1">
+        <v>50</v>
+      </c>
+      <c r="AM1" t="s" s="1">
+        <v>51</v>
+      </c>
+      <c r="AN1" t="s" s="1">
+        <v>52</v>
+      </c>
+      <c r="AO1" t="s" s="1">
+        <v>53</v>
+      </c>
+      <c r="AP1" t="s" s="1">
+        <v>54</v>
+      </c>
+      <c r="AQ1" t="s" s="1">
+        <v>55</v>
+      </c>
+      <c r="AR1" t="s" s="1">
+        <v>56</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
@@ -443,42 +766,104 @@
       <c r="C2" t="s" s="0">
         <v>12</v>
       </c>
-      <c r="D2" t="n" s="4">
+      <c r="D2" t="n" s="7">
         <v>72.5</v>
       </c>
       <c r="E2" t="s" s="0">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="F2" t="s" s="0">
         <v>13</v>
       </c>
       <c r="G2" t="s" s="0">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="H2" t="s" s="0">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="I2" t="s" s="0">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="J2" s="0"/>
       <c r="K2" s="0"/>
-      <c r="L2" s="0"/>
-      <c r="M2" s="0"/>
+      <c r="L2" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="M2" t="n" s="7">
+        <v>22950.0</v>
+      </c>
       <c r="N2" s="0"/>
-      <c r="O2" t="s" s="0">
-        <v>36</v>
-      </c>
-      <c r="P2" t="s" s="0">
-        <v>36</v>
-      </c>
-      <c r="Q2" s="0"/>
-      <c r="R2" s="0"/>
-      <c r="S2" t="s" s="0">
-        <v>36</v>
-      </c>
-      <c r="T2" t="s" s="0">
-        <v>36</v>
+      <c r="O2" s="0"/>
+      <c r="P2" s="0"/>
+      <c r="Q2" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="R2" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="S2" s="0"/>
+      <c r="T2" s="0"/>
+      <c r="U2" t="n" s="7">
+        <v>100.25</v>
+      </c>
+      <c r="V2" t="n" s="7">
+        <v>101.25</v>
+      </c>
+      <c r="W2" t="n" s="7">
+        <v>102.25</v>
+      </c>
+      <c r="X2" t="n" s="7">
+        <v>103.25</v>
+      </c>
+      <c r="Y2" t="n" s="7">
+        <v>104.25</v>
+      </c>
+      <c r="Z2" t="n" s="7">
+        <v>105.25</v>
+      </c>
+      <c r="AA2" t="n" s="7">
+        <v>106.25</v>
+      </c>
+      <c r="AB2" t="n" s="7">
+        <v>107.25</v>
+      </c>
+      <c r="AC2" t="n" s="7">
+        <v>108.25</v>
+      </c>
+      <c r="AD2" t="n" s="7">
+        <v>109.25</v>
+      </c>
+      <c r="AE2" t="n" s="7">
+        <v>110.25</v>
+      </c>
+      <c r="AF2" t="n" s="7">
+        <v>111.25</v>
+      </c>
+      <c r="AG2" t="n" s="7">
+        <v>112.25</v>
+      </c>
+      <c r="AH2" t="n" s="7">
+        <v>113.25</v>
+      </c>
+      <c r="AI2" s="0"/>
+      <c r="AJ2" s="0"/>
+      <c r="AK2" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="AL2" s="0"/>
+      <c r="AM2" s="0"/>
+      <c r="AN2" s="0"/>
+      <c r="AO2" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="AP2" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="AQ2" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="AR2" t="s" s="0">
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -488,7 +873,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AI2"/>
+  <dimension ref="A1:CJ2"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="18.73046875" customWidth="true" bestFit="true"/>
@@ -498,34 +883,87 @@
     <col min="5" max="5" width="7.2890625" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.12890625" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="7.2890625" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="5.3203125" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="7.2890625" customWidth="true" bestFit="true"/>
-    <col min="10" max="10" width="5.40234375" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="7.2890625" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="10.453125" customWidth="true" bestFit="true"/>
+    <col min="10" max="10" width="7.2890625" customWidth="true" bestFit="true"/>
     <col min="11" max="11" width="7.2890625" customWidth="true" bestFit="true"/>
-    <col min="12" max="12" width="7.2890625" customWidth="true" bestFit="true"/>
-    <col min="13" max="13" width="7.90234375" customWidth="true" bestFit="true"/>
-    <col min="14" max="14" width="5.3671875" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="7.2890625" customWidth="true" bestFit="true"/>
-    <col min="16" max="16" width="6.83203125" customWidth="true" bestFit="true"/>
-    <col min="17" max="17" width="5.65234375" customWidth="true" bestFit="true"/>
-    <col min="18" max="18" width="5.65234375" customWidth="true" bestFit="true"/>
-    <col min="19" max="19" width="6.6953125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="7.2890625" customWidth="true" bestFit="true"/>
+    <col min="12" max="12" width="10.453125" customWidth="true" bestFit="true"/>
+    <col min="13" max="13" width="7.2890625" customWidth="true" bestFit="true"/>
+    <col min="14" max="14" width="8.87109375" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="10.453125" customWidth="true" bestFit="true"/>
+    <col min="16" max="16" width="7.2890625" customWidth="true" bestFit="true"/>
+    <col min="17" max="17" width="7.2890625" customWidth="true" bestFit="true"/>
+    <col min="18" max="18" width="7.90234375" customWidth="true" bestFit="true"/>
+    <col min="19" max="19" width="5.3671875" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="13.2578125" customWidth="true" bestFit="true"/>
     <col min="21" max="21" width="7.2890625" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="7.2890625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="2.0859375" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="2.21875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="7.2890625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="7.2890625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="6.83203125" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="7.90234375" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="5.65234375" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="5.65234375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="6.6953125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="7.2890625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="7.2265625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="8.52734375" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="7.796875" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="6.94921875" customWidth="true" bestFit="true"/>
-    <col min="32" max="32" width="7.2890625" customWidth="true" bestFit="true"/>
-    <col min="33" max="33" width="7.2890625" customWidth="true" bestFit="true"/>
-    <col min="34" max="34" width="7.2890625" customWidth="true" bestFit="true"/>
-    <col min="35" max="35" width="7.2890625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="7.2890625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="7.2890625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="2.0859375" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="2.21875" customWidth="true" bestFit="true"/>
+    <col min="32" max="32" width="6.40234375" customWidth="true" bestFit="true"/>
+    <col min="33" max="33" width="6.40234375" customWidth="true" bestFit="true"/>
+    <col min="34" max="34" width="6.40234375" customWidth="true" bestFit="true"/>
+    <col min="35" max="35" width="6.6015625" customWidth="true" bestFit="true"/>
+    <col min="36" max="36" width="6.6015625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="6.40234375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="6.40234375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="6.40234375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="6.40234375" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="6.40234375" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="6.640625" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="6.640625" customWidth="true" bestFit="true"/>
+    <col min="44" max="44" width="13.32421875" customWidth="true" bestFit="true"/>
+    <col min="45" max="45" width="6.40234375" customWidth="true" bestFit="true"/>
+    <col min="46" max="46" width="7.2890625" customWidth="true" bestFit="true"/>
+    <col min="47" max="47" width="7.2890625" customWidth="true" bestFit="true"/>
+    <col min="48" max="48" width="8.87109375" customWidth="true" bestFit="true"/>
+    <col min="49" max="49" width="7.2890625" customWidth="true" bestFit="true"/>
+    <col min="50" max="50" width="7.2890625" customWidth="true" bestFit="true"/>
+    <col min="51" max="51" width="7.2265625" customWidth="true" bestFit="true"/>
+    <col min="52" max="52" width="8.52734375" customWidth="true" bestFit="true"/>
+    <col min="53" max="53" width="7.796875" customWidth="true" bestFit="true"/>
+    <col min="54" max="54" width="6.94921875" customWidth="true" bestFit="true"/>
+    <col min="55" max="55" width="8.87109375" customWidth="true" bestFit="true"/>
+    <col min="56" max="56" width="13.140625" customWidth="true" bestFit="true"/>
+    <col min="57" max="57" width="12.328125" customWidth="true" bestFit="true"/>
+    <col min="58" max="58" width="6.94921875" customWidth="true" bestFit="true"/>
+    <col min="59" max="59" width="10.11328125" customWidth="true" bestFit="true"/>
+    <col min="60" max="60" width="10.11328125" customWidth="true" bestFit="true"/>
+    <col min="61" max="61" width="8.70703125" customWidth="true" bestFit="true"/>
+    <col min="62" max="62" width="7.46875" customWidth="true" bestFit="true"/>
+    <col min="63" max="63" width="10.6328125" customWidth="true" bestFit="true"/>
+    <col min="64" max="64" width="10.6328125" customWidth="true" bestFit="true"/>
+    <col min="65" max="65" width="12.734375" customWidth="true" bestFit="true"/>
+    <col min="66" max="66" width="7.2890625" customWidth="true" bestFit="true"/>
+    <col min="67" max="67" width="10.453125" customWidth="true" bestFit="true"/>
+    <col min="68" max="68" width="10.453125" customWidth="true" bestFit="true"/>
+    <col min="69" max="69" width="9.2109375" customWidth="true" bestFit="true"/>
+    <col min="70" max="70" width="9.2109375" customWidth="true" bestFit="true"/>
+    <col min="71" max="71" width="7.2890625" customWidth="true" bestFit="true"/>
+    <col min="72" max="72" width="10.453125" customWidth="true" bestFit="true"/>
+    <col min="73" max="73" width="10.453125" customWidth="true" bestFit="true"/>
+    <col min="74" max="74" width="4.12890625" customWidth="true" bestFit="true"/>
+    <col min="75" max="75" width="11.69140625" customWidth="true" bestFit="true"/>
+    <col min="76" max="76" width="8.87109375" customWidth="true" bestFit="true"/>
+    <col min="77" max="77" width="10.453125" customWidth="true" bestFit="true"/>
+    <col min="78" max="78" width="7.2890625" customWidth="true" bestFit="true"/>
+    <col min="79" max="79" width="10.453125" customWidth="true" bestFit="true"/>
+    <col min="80" max="80" width="10.453125" customWidth="true" bestFit="true"/>
+    <col min="81" max="81" width="17.83203125" customWidth="true" bestFit="true"/>
+    <col min="82" max="82" width="17.83203125" customWidth="true" bestFit="true"/>
+    <col min="83" max="83" width="10.453125" customWidth="true" bestFit="true"/>
+    <col min="84" max="84" width="10.453125" customWidth="true" bestFit="true"/>
+    <col min="85" max="85" width="10.453125" customWidth="true" bestFit="true"/>
+    <col min="86" max="86" width="10.453125" customWidth="true" bestFit="true"/>
+    <col min="87" max="87" width="7.2890625" customWidth="true" bestFit="true"/>
+    <col min="88" max="88" width="7.2890625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -533,106 +971,265 @@
         <v>1</v>
       </c>
       <c r="B1" t="s" s="1">
+        <v>62</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>63</v>
+      </c>
+      <c r="D1" t="s" s="1">
+        <v>64</v>
+      </c>
+      <c r="E1" t="s" s="1">
+        <v>65</v>
+      </c>
+      <c r="F1" t="s" s="1">
+        <v>66</v>
+      </c>
+      <c r="G1" t="s" s="1">
+        <v>67</v>
+      </c>
+      <c r="H1" t="s" s="1">
+        <v>68</v>
+      </c>
+      <c r="I1" t="s" s="1">
+        <v>69</v>
+      </c>
+      <c r="J1" t="s" s="1">
+        <v>70</v>
+      </c>
+      <c r="K1" t="s" s="1">
+        <v>71</v>
+      </c>
+      <c r="L1" t="s" s="1">
+        <v>72</v>
+      </c>
+      <c r="M1" t="s" s="1">
+        <v>73</v>
+      </c>
+      <c r="N1" t="s" s="1">
+        <v>74</v>
+      </c>
+      <c r="O1" t="s" s="1">
+        <v>75</v>
+      </c>
+      <c r="P1" t="s" s="1">
+        <v>76</v>
+      </c>
+      <c r="Q1" t="s" s="1">
+        <v>77</v>
+      </c>
+      <c r="R1" t="s" s="1">
+        <v>78</v>
+      </c>
+      <c r="S1" t="s" s="1">
+        <v>23</v>
+      </c>
+      <c r="T1" t="s" s="1">
+        <v>24</v>
+      </c>
+      <c r="U1" t="s" s="1">
+        <v>79</v>
+      </c>
+      <c r="V1" t="s" s="1">
+        <v>21</v>
+      </c>
+      <c r="W1" t="s" s="1">
+        <v>25</v>
+      </c>
+      <c r="X1" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="Y1" t="s" s="1">
+        <v>27</v>
+      </c>
+      <c r="Z1" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="AA1" t="s" s="1">
+        <v>80</v>
+      </c>
+      <c r="AB1" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="AC1" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="AD1" t="s" s="1">
+        <v>31</v>
+      </c>
+      <c r="AE1" t="s" s="1">
+        <v>32</v>
+      </c>
+      <c r="AF1" t="s" s="1">
+        <v>33</v>
+      </c>
+      <c r="AG1" t="s" s="1">
+        <v>34</v>
+      </c>
+      <c r="AH1" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="AI1" t="s" s="1">
+        <v>36</v>
+      </c>
+      <c r="AJ1" t="s" s="1">
         <v>37</v>
       </c>
-      <c r="C1" t="s" s="1">
+      <c r="AK1" t="s" s="1">
         <v>38</v>
       </c>
-      <c r="D1" t="s" s="1">
+      <c r="AL1" t="s" s="1">
         <v>39</v>
       </c>
-      <c r="E1" t="s" s="1">
+      <c r="AM1" t="s" s="1">
         <v>40</v>
       </c>
-      <c r="F1" t="s" s="1">
+      <c r="AN1" t="s" s="1">
         <v>41</v>
       </c>
-      <c r="G1" t="s" s="1">
+      <c r="AO1" t="s" s="1">
         <v>42</v>
       </c>
-      <c r="H1" t="s" s="1">
+      <c r="AP1" t="s" s="1">
         <v>43</v>
       </c>
-      <c r="I1" t="s" s="1">
+      <c r="AQ1" t="s" s="1">
         <v>44</v>
       </c>
-      <c r="J1" t="s" s="1">
-        <v>16</v>
-      </c>
-      <c r="K1" t="s" s="1">
+      <c r="AR1" t="s" s="1">
         <v>45</v>
       </c>
-      <c r="L1" t="s" s="1">
+      <c r="AS1" t="s" s="1">
         <v>46</v>
       </c>
-      <c r="M1" t="s" s="1">
-        <v>47</v>
-      </c>
-      <c r="N1" t="s" s="1">
-        <v>23</v>
-      </c>
-      <c r="O1" t="s" s="1">
-        <v>48</v>
-      </c>
-      <c r="P1" t="s" s="1">
-        <v>21</v>
-      </c>
-      <c r="Q1" t="s" s="1">
-        <v>24</v>
-      </c>
-      <c r="R1" t="s" s="1">
-        <v>25</v>
-      </c>
-      <c r="S1" t="s" s="1">
-        <v>26</v>
-      </c>
-      <c r="T1" t="s" s="1">
-        <v>49</v>
-      </c>
-      <c r="U1" t="s" s="1">
-        <v>27</v>
-      </c>
-      <c r="V1" t="s" s="1">
-        <v>28</v>
-      </c>
-      <c r="W1" t="s" s="1">
-        <v>29</v>
-      </c>
-      <c r="X1" t="s" s="1">
-        <v>30</v>
-      </c>
-      <c r="Y1" t="s" s="1">
-        <v>50</v>
-      </c>
-      <c r="Z1" t="s" s="1">
-        <v>51</v>
-      </c>
-      <c r="AA1" t="s" s="1">
+      <c r="AT1" t="s" s="1">
+        <v>81</v>
+      </c>
+      <c r="AU1" t="s" s="1">
+        <v>82</v>
+      </c>
+      <c r="AV1" t="s" s="1">
+        <v>83</v>
+      </c>
+      <c r="AW1" t="s" s="1">
+        <v>84</v>
+      </c>
+      <c r="AX1" t="s" s="1">
         <v>17</v>
       </c>
-      <c r="AB1" t="s" s="1">
-        <v>52</v>
-      </c>
-      <c r="AC1" t="s" s="1">
-        <v>53</v>
-      </c>
-      <c r="AD1" t="s" s="1">
-        <v>54</v>
-      </c>
-      <c r="AE1" t="s" s="1">
-        <v>55</v>
-      </c>
-      <c r="AF1" t="s" s="1">
-        <v>31</v>
-      </c>
-      <c r="AG1" t="s" s="1">
-        <v>32</v>
-      </c>
-      <c r="AH1" t="s" s="1">
-        <v>56</v>
-      </c>
-      <c r="AI1" t="s" s="1">
-        <v>57</v>
+      <c r="AY1" t="s" s="1">
+        <v>85</v>
+      </c>
+      <c r="AZ1" t="s" s="1">
+        <v>86</v>
+      </c>
+      <c r="BA1" t="s" s="1">
+        <v>87</v>
+      </c>
+      <c r="BB1" t="s" s="1">
+        <v>88</v>
+      </c>
+      <c r="BC1" t="s" s="1">
+        <v>89</v>
+      </c>
+      <c r="BD1" t="s" s="1">
+        <v>90</v>
+      </c>
+      <c r="BE1" t="s" s="1">
+        <v>91</v>
+      </c>
+      <c r="BF1" t="s" s="1">
+        <v>92</v>
+      </c>
+      <c r="BG1" t="s" s="1">
+        <v>93</v>
+      </c>
+      <c r="BH1" t="s" s="1">
+        <v>94</v>
+      </c>
+      <c r="BI1" t="s" s="1">
+        <v>95</v>
+      </c>
+      <c r="BJ1" t="s" s="1">
+        <v>96</v>
+      </c>
+      <c r="BK1" t="s" s="1">
+        <v>97</v>
+      </c>
+      <c r="BL1" t="s" s="1">
+        <v>98</v>
+      </c>
+      <c r="BM1" t="s" s="1">
+        <v>99</v>
+      </c>
+      <c r="BN1" t="s" s="1">
+        <v>100</v>
+      </c>
+      <c r="BO1" t="s" s="1">
+        <v>101</v>
+      </c>
+      <c r="BP1" t="s" s="1">
+        <v>102</v>
+      </c>
+      <c r="BQ1" t="s" s="1">
+        <v>103</v>
+      </c>
+      <c r="BR1" t="s" s="1">
+        <v>104</v>
+      </c>
+      <c r="BS1" t="s" s="1">
+        <v>105</v>
+      </c>
+      <c r="BT1" t="s" s="1">
+        <v>106</v>
+      </c>
+      <c r="BU1" t="s" s="1">
+        <v>107</v>
+      </c>
+      <c r="BV1" t="s" s="1">
+        <v>108</v>
+      </c>
+      <c r="BW1" t="s" s="1">
+        <v>109</v>
+      </c>
+      <c r="BX1" t="s" s="1">
+        <v>110</v>
+      </c>
+      <c r="BY1" t="s" s="1">
+        <v>111</v>
+      </c>
+      <c r="BZ1" t="s" s="1">
+        <v>112</v>
+      </c>
+      <c r="CA1" t="s" s="1">
+        <v>113</v>
+      </c>
+      <c r="CB1" t="s" s="1">
+        <v>114</v>
+      </c>
+      <c r="CC1" t="s" s="1">
+        <v>115</v>
+      </c>
+      <c r="CD1" t="s" s="1">
+        <v>116</v>
+      </c>
+      <c r="CE1" t="s" s="1">
+        <v>117</v>
+      </c>
+      <c r="CF1" t="s" s="1">
+        <v>118</v>
+      </c>
+      <c r="CG1" t="s" s="1">
+        <v>119</v>
+      </c>
+      <c r="CH1" t="s" s="1">
+        <v>120</v>
+      </c>
+      <c r="CI1" t="s" s="1">
+        <v>121</v>
+      </c>
+      <c r="CJ1" t="s" s="1">
+        <v>122</v>
       </c>
     </row>
     <row r="2">
@@ -640,90 +1237,273 @@
         <v>9</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>58</v>
+        <v>123</v>
       </c>
       <c r="E2" t="s" s="0">
-        <v>59</v>
+        <v>124</v>
       </c>
       <c r="F2" t="s" s="0">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="G2" t="s" s="0">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="H2" t="s" s="0">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I2" t="s" s="0">
         <v>61</v>
       </c>
-      <c r="J2" t="n" s="4">
+      <c r="J2" s="0"/>
+      <c r="K2" t="s" s="0">
+        <v>125</v>
+      </c>
+      <c r="L2" t="s" s="0">
+        <v>126</v>
+      </c>
+      <c r="M2" t="n" s="7">
         <v>61.0</v>
       </c>
-      <c r="K2" t="s" s="0">
-        <v>36</v>
-      </c>
-      <c r="L2" t="s" s="0">
-        <v>36</v>
-      </c>
-      <c r="M2" t="n" s="4">
+      <c r="N2" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="O2" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="P2" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="Q2" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="R2" t="n" s="7">
         <v>1105.0</v>
       </c>
-      <c r="N2" s="0"/>
-      <c r="O2" t="s" s="0">
-        <v>36</v>
-      </c>
-      <c r="P2" t="s" s="0">
-        <v>36</v>
-      </c>
-      <c r="Q2" s="0"/>
-      <c r="R2" s="0"/>
       <c r="S2" s="0"/>
       <c r="T2" t="s" s="0">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="U2" t="s" s="0">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="V2" t="s" s="0">
-        <v>36</v>
-      </c>
-      <c r="W2" s="0"/>
+        <v>61</v>
+      </c>
+      <c r="W2" t="n" s="7">
+        <v>1102.5</v>
+      </c>
       <c r="X2" s="0"/>
       <c r="Y2" s="0"/>
-      <c r="Z2" t="s" s="0">
-        <v>36</v>
-      </c>
+      <c r="Z2" s="0"/>
       <c r="AA2" t="s" s="0">
-        <v>33</v>
+        <v>61</v>
       </c>
       <c r="AB2" t="s" s="0">
-        <v>62</v>
-      </c>
-      <c r="AC2" t="n" s="4">
+        <v>61</v>
+      </c>
+      <c r="AC2" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="AD2" s="0"/>
+      <c r="AE2" s="0"/>
+      <c r="AF2" t="n" s="7">
+        <v>200.25</v>
+      </c>
+      <c r="AG2" t="n" s="7">
+        <v>201.25</v>
+      </c>
+      <c r="AH2" t="n" s="7">
+        <v>202.25</v>
+      </c>
+      <c r="AI2" t="n" s="7">
+        <v>203.25</v>
+      </c>
+      <c r="AJ2" t="n" s="7">
+        <v>204.25</v>
+      </c>
+      <c r="AK2" t="n" s="7">
+        <v>205.25</v>
+      </c>
+      <c r="AL2" t="n" s="7">
+        <v>206.25</v>
+      </c>
+      <c r="AM2" t="n" s="7">
+        <v>207.25</v>
+      </c>
+      <c r="AN2" t="n" s="7">
+        <v>208.25</v>
+      </c>
+      <c r="AO2" t="n" s="7">
+        <v>209.25</v>
+      </c>
+      <c r="AP2" t="n" s="7">
+        <v>210.25</v>
+      </c>
+      <c r="AQ2" t="n" s="7">
+        <v>211.25</v>
+      </c>
+      <c r="AR2" t="n" s="7">
+        <v>212.25</v>
+      </c>
+      <c r="AS2" t="n" s="7">
+        <v>213.25</v>
+      </c>
+      <c r="AT2" s="0"/>
+      <c r="AU2" s="0"/>
+      <c r="AV2" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="AW2" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="AX2" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="AY2" t="s" s="0">
+        <v>127</v>
+      </c>
+      <c r="AZ2" t="n" s="7">
         <v>12.75</v>
       </c>
-      <c r="AD2" t="n" s="4">
+      <c r="BA2" t="n" s="7">
         <v>88.5</v>
       </c>
-      <c r="AE2" s="0"/>
-      <c r="AF2" t="s" s="0">
-        <v>36</v>
-      </c>
-      <c r="AG2" t="s" s="0">
-        <v>36</v>
-      </c>
-      <c r="AH2" t="s" s="0">
-        <v>36</v>
-      </c>
-      <c r="AI2" t="s" s="0">
-        <v>36</v>
+      <c r="BB2" s="0"/>
+      <c r="BC2" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="BD2" s="0"/>
+      <c r="BE2" s="0"/>
+      <c r="BF2" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="BG2" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="BH2" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="BI2" s="0"/>
+      <c r="BJ2" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="BK2" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="BL2" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="BM2" s="0"/>
+      <c r="BN2" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="BO2" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="BP2" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="BQ2" s="0"/>
+      <c r="BR2" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="BS2" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="BT2" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="BU2" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="BV2" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="BW2" s="0"/>
+      <c r="BX2" s="0"/>
+      <c r="BY2" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="BZ2" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="CA2" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="CB2" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="CC2" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="CD2" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="CE2" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="CF2" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="CG2" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="CH2" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="CI2" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="CJ2" t="s" s="0">
+        <v>61</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:G1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="7.2890625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="4.12890625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="7.2890625" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="4.12890625" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="4.12890625" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.12890625" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.12890625" customWidth="true" bestFit="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>128</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>129</v>
+      </c>
+      <c r="D1" t="s" s="1">
+        <v>130</v>
+      </c>
+      <c r="E1" t="s" s="1">
+        <v>131</v>
+      </c>
+      <c r="F1" t="s" s="1">
+        <v>132</v>
+      </c>
+      <c r="G1" t="s" s="1">
+        <v>133</v>
       </c>
     </row>
   </sheetData>
